--- a/Caleb_territory_chart2.xlsx
+++ b/Caleb_territory_chart2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/81ca02095870d75e/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/81ca02095870d75e/Documents/DATA_Labs/Capstone_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{E442D6F5-DB9B-4566-B358-D8B3D89EBD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="236" documentId="14_{E442D6F5-DB9B-4566-B358-D8B3D89EBD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F343BD4-4D7F-496B-AA5E-56C9C6794207}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{BB745B30-7400-441B-81F5-EE7C431BA921}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{BB745B30-7400-441B-81F5-EE7C431BA921}"/>
   </bookViews>
   <sheets>
     <sheet name="Caleb_territory_chart2" sheetId="1" r:id="rId1"/>
@@ -18,16 +18,17 @@
     <sheet name="comparing_categories" sheetId="3" r:id="rId3"/>
     <sheet name="trends_overtime" sheetId="4" r:id="rId4"/>
     <sheet name="performance_by_transaction" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="81">
   <si>
     <t>Sales_Month</t>
   </si>
@@ -256,6 +257,21 @@
   <si>
     <t>The chart  indicate a remarkable increase or improvement over time as seen from  2022 through 2025</t>
   </si>
+  <si>
+    <t>cdcc</t>
+  </si>
+  <si>
+    <t>Sum of Number_Of_Transactions</t>
+  </si>
+  <si>
+    <t>Total Revenue</t>
+  </si>
+  <si>
+    <t>Total Transactins</t>
+  </si>
+  <si>
+    <t>EmperiUm Dash Board Wes Region Colorado</t>
+  </si>
 </sst>
 </file>
 
@@ -407,7 +423,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -587,6 +603,24 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -748,7 +782,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -761,10 +795,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -837,7 +883,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Caleb_territory_chart2.xlsx]comparing_categories!PivotTable1</c:name>
+    <c:name>[caleb_territory_chart2.xlsx]comparing_categories!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -1308,7 +1354,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Caleb_territory_chart2.xlsx]comparing_categories!PivotTable2</c:name>
+    <c:name>[caleb_territory_chart2.xlsx]comparing_categories!PivotTable2</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -1692,22 +1738,22 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>Stationery and Supplies</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Books (General)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Art Supplies</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Apparel and Merchandise</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>Art Supplies</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Books (General)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Stationery and Supplies</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>Technology &amp; Accessories</c:v>
+                  <c:v>Textbooks</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Textbooks</c:v>
+                  <c:v>Technology &amp; Accessories</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1719,22 +1765,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>98482.62000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>107407.42000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>239912.40999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>299559.51</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>239912.40999999995</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>107407.42000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>98482.62000000001</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>4554123.47</c:v>
+                  <c:v>1113146.79</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1113146.79</c:v>
+                  <c:v>4554123.47</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1870,7 +1916,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Caleb_territory_chart2.xlsx]trends_overtime!PivotTable3</c:name>
+    <c:name>[caleb_territory_chart2.xlsx]trends_overtime!PivotTable3</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -1995,6 +2041,287 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout>
@@ -2008,9 +2335,8 @@
           <c:h val="0.58196485855934676"/>
         </c:manualLayout>
       </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -2027,18 +2353,17 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3">
-                <a:lumMod val="60000"/>
-                <a:lumOff val="40000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:multiLvlStrRef>
               <c:f>trends_overtime!$A$2:$A$22</c:f>
@@ -2168,9 +2493,10 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8C1B-4576-92B2-9D407FB7663A}"/>
+              <c16:uniqueId val="{00000003-1FAF-4234-887C-80147BB9C11A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2182,11 +2508,10 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
+        <c:smooth val="0"/>
         <c:axId val="1464131184"/>
         <c:axId val="1464133104"/>
-      </c:barChart>
+      </c:lineChart>
       <c:catAx>
         <c:axId val="1464131184"/>
         <c:scaling>
@@ -2195,7 +2520,7 @@
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -2260,7 +2585,7 @@
           </c:spPr>
         </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -2302,37 +2627,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -2380,7 +2674,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -2407,7 +2700,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Caleb_territory_chart2.xlsx]performance_by_transaction!PivotTable4</c:name>
+    <c:name>[caleb_territory_chart2.xlsx]performance_by_transaction!PivotTable4</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -2696,7 +2989,7 @@
         <c:idx val="4"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent4"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -2706,47 +2999,24 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
             <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -2764,14 +3034,14 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>Sum of Average_Transaction_Size</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2838,7 +3108,94 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>performance_by_transaction!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Number_Of_Transactions</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>performance_by_transaction!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Stationery and Supplies</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Books (General)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Art Supplies</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apparel and Merchandise</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Textbooks</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Technology &amp; Accessories</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>performance_by_transaction!$C$2:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>9776</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3734</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7551</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9203</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6428</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9806</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9A74-4F2A-9AFA-021AA7533078}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -3057,6 +3414,3329 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[caleb_territory_chart2.xlsx]performance_by_transaction!PivotTable4</c:name>
+    <c:fmtId val="5"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Category Performance</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>performance_by_transaction!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Average_Transaction_Size</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>performance_by_transaction!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Stationery and Supplies</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Books (General)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Art Supplies</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apparel and Merchandise</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Textbooks</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Technology &amp; Accessories</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>performance_by_transaction!$B$2:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>483.40523000000007</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1368.2435330000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1487.9836310000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1557.1017999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8336.4585240000015</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>22058.841376000004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-83C5-46BA-81EA-3B66A602C270}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>performance_by_transaction!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Number_Of_Transactions</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>performance_by_transaction!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Stationery and Supplies</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Books (General)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Art Supplies</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apparel and Merchandise</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Textbooks</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Technology &amp; Accessories</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>performance_by_transaction!$C$2:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>9776</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3734</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7551</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9203</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6428</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9806</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-83C5-46BA-81EA-3B66A602C270}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="200427952"/>
+        <c:axId val="200425552"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="200427952"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="200425552"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="200425552"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="200427952"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="tx2">
+        <a:lumMod val="10000"/>
+        <a:lumOff val="90000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[caleb_territory_chart2.xlsx]trends_overtime!PivotTable3</c:name>
+    <c:fmtId val="13"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Growth</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Over Time</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12377821522309711"/>
+          <c:y val="0.17490522018081076"/>
+          <c:w val="0.73816426071741037"/>
+          <c:h val="0.58196485855934676"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>trends_overtime!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>trends_overtime!$A$2:$A$22</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="16"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Qtr1</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Qtr2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Qtr3</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Qtr4</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Qtr1</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Qtr2</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Qtr3</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Qtr4</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Qtr1</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qtr2</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Qtr3</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Qtr4</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Qtr1</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Qtr2</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>Qtr3</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>Qtr4</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2022</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>2023</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>2024</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>2025</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>trends_overtime!$B$2:$B$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>240783.03000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>271090.90000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>265312.93999999994</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>234168.65</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>358599.23999999993</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>368782.32999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>407029.68</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>353479.47000000003</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>368886.83999999997</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>372044.97000000003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>388872.14</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>361663.86</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>529876.55999999994</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>522419.16</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>610347.14999999991</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>759275.30000000016</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-515D-452B-BEC8-8C284A343C8B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1464131184"/>
+        <c:axId val="1464133104"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1464131184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1464133104"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1464133104"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1464131184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="tx2">
+        <a:lumMod val="10000"/>
+        <a:lumOff val="90000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[caleb_territory_chart2.xlsx]comparing_categories!PivotTable2</c:name>
+    <c:fmtId val="7"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue By</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Category</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="14"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="15"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="16"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="17"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="18"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="19"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="20"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>comparing_categories!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-418A-421F-860F-A0C28F9F92D5}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-418A-421F-860F-A0C28F9F92D5}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-418A-421F-860F-A0C28F9F92D5}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-418A-421F-860F-A0C28F9F92D5}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-418A-421F-860F-A0C28F9F92D5}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-418A-421F-860F-A0C28F9F92D5}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="bestFit"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>comparing_categories!$G$2:$G$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Stationery and Supplies</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Books (General)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Art Supplies</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apparel and Merchandise</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Textbooks</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Technology &amp; Accessories</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>comparing_categories!$H$2:$H$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>98482.62000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>107407.42000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>239912.40999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>299559.51</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1113146.79</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4554123.47</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-418A-421F-860F-A0C28F9F92D5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="tx2">
+        <a:lumMod val="10000"/>
+        <a:lumOff val="90000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[caleb_territory_chart2.xlsx]comparing_categories!PivotTable1</c:name>
+    <c:fmtId val="5"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> By Category</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.15584500535563894"/>
+          <c:y val="0.22124733022562865"/>
+          <c:w val="0.6982432686568385"/>
+          <c:h val="0.40041552455610452"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>comparing_categories!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>comparing_categories!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Technology &amp; Accessories</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Textbooks</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Apparel and Merchandise</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Art Supplies</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Books (General)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Stationery and Supplies</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>comparing_categories!$B$2:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>4554123.47</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1113146.79</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>299559.51</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>239912.40999999995</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>107407.42000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>98482.62000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-630A-48A7-9913-50AAC19387AE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1336499968"/>
+        <c:axId val="1336499488"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1336499968"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1336499488"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1336499488"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1336499968"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="tx2">
+        <a:lumMod val="10000"/>
+        <a:lumOff val="90000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -3178,6 +6858,166 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -5229,6 +9069,2018 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -5269,16 +11121,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>118110</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>541020</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>118110</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5310,16 +11162,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>601980</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>297180</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5352,15 +11204,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>480060</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5388,8 +11240,161 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC05ADC7-E05F-4311-85CF-746717337F0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{494D50DE-EE16-48C6-9A7B-0592A2B340E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53527ECF-6A9D-4DC1-B76C-75B5B022EDB4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C198A7F-9B4F-4FEC-A024-0486D38A3D95}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7548,7 +13553,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D34989FF-5BE8-4161-9C32-B61649ED12F5}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D34989FF-5BE8-4161-9C32-B61649ED12F5}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="G1:H8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField numFmtId="164" showAll="0">
@@ -7604,7 +13609,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
       <items count="7">
         <item x="2"/>
         <item x="3"/>
@@ -7614,6 +13619,15 @@
         <item x="1"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -7665,22 +13679,22 @@
   </rowFields>
   <rowItems count="7">
     <i>
-      <x/>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
     </i>
     <i>
       <x v="1"/>
     </i>
     <i>
-      <x v="2"/>
+      <x/>
     </i>
     <i>
-      <x v="3"/>
+      <x v="5"/>
     </i>
     <i>
       <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -7692,7 +13706,7 @@
   <dataFields count="1">
     <dataField name="Sum of Total_Revenue" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="7">
+  <chartFormats count="14">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -7774,6 +13788,87 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="7" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="15">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="16">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="17">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="18">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="19">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="20">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -7788,7 +13883,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6DA80A0-CB47-42C3-851A-84988BA97CE4}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6DA80A0-CB47-42C3-851A-84988BA97CE4}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="A1:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField numFmtId="164" showAll="0">
@@ -7941,8 +14036,35 @@
   <dataFields count="1">
     <dataField name="Sum of Total_Revenue" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="4">
     <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -7965,7 +14087,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F39CBDC-373C-4E07-91D4-8EB931B6C31A}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F39CBDC-373C-4E07-91D4-8EB931B6C31A}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
   <location ref="A1:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" numFmtId="164" showAll="0">
@@ -8021,7 +14143,17 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -8055,7 +14187,7 @@
         <item t="default" sd="0"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+    <pivotField axis="axisRow" showAll="0">
       <items count="7">
         <item x="0"/>
         <item x="1"/>
@@ -8065,15 +14197,6 @@
         <item x="5"/>
         <item t="default"/>
       </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
     </pivotField>
   </pivotFields>
   <rowFields count="4">
@@ -8153,8 +14276,17 @@
   <dataFields count="1">
     <dataField name="Sum of Total_Revenue" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
+  <chartFormats count="2">
+    <chartFormat chart="0" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="7" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8177,8 +14309,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B2882FD3-0312-4592-B641-2506126231B7}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A1:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B2882FD3-0312-4592-B641-2506126231B7}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="A1:C8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField numFmtId="164" showAll="0">
       <items count="49">
@@ -8253,7 +14385,7 @@
         </pivotArea>
       </autoSortScope>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
@@ -8295,18 +14427,54 @@
       <x/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
   </colItems>
-  <dataFields count="1">
+  <dataFields count="2">
     <dataField name="Sum of Average_Transaction_Size" fld="3" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Number_Of_Transactions" fld="2" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="4">
     <chartFormat chart="0" format="4" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
@@ -18494,7 +24662,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6CB0FF6-5285-451C-974E-3CFC9CE910BF}">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
@@ -18503,7 +24671,7 @@
     <col min="8" max="8" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -18517,7 +24685,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -18525,13 +24693,13 @@
         <v>4554123.47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2">
-        <v>299559.51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="H2" s="7">
+        <v>98482.62000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -18539,10 +24707,10 @@
         <v>1113146.79</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>239912.40999999995</v>
+        <v>11</v>
+      </c>
+      <c r="H3" s="7">
+        <v>107407.42000000001</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>71</v>
@@ -18553,7 +24721,7 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -18561,10 +24729,10 @@
         <v>299559.51</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4">
-        <v>107407.42000000001</v>
+        <v>9</v>
+      </c>
+      <c r="H4" s="7">
+        <v>239912.40999999995</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -18573,7 +24741,7 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -18581,21 +24749,16 @@
         <v>239912.40999999995</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5">
-        <v>98482.62000000001</v>
-      </c>
-      <c r="M5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="7">
+        <v>299559.51</v>
+      </c>
+      <c r="M5" t="s">
         <v>72</v>
       </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
@@ -18603,21 +24766,16 @@
         <v>107407.42000000001</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>4554123.47</v>
-      </c>
-      <c r="M6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="7">
+        <v>1113146.79</v>
+      </c>
+      <c r="M6" t="s">
         <v>73</v>
       </c>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -18625,21 +24783,16 @@
         <v>98482.62000000001</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7">
-        <v>1113146.79</v>
-      </c>
-      <c r="M7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="7">
+        <v>4554123.47</v>
+      </c>
+      <c r="M7" t="s">
         <v>74</v>
       </c>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>60</v>
       </c>
@@ -18649,13 +24802,26 @@
       <c r="G8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="7">
         <v>6412632.2199999997</v>
       </c>
     </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="L11" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="M3:R4"/>
+    <mergeCell ref="L11:S11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId3"/>
@@ -18664,14 +24830,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42DB78C8-DCF3-4C75-A847-0BDE367EDBBA}">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -18679,136 +24846,136 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="7">
         <v>1011355.52</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="7">
         <v>240783.03000000003</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="H3" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>271090.90000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>265312.93999999994</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="7">
         <v>234168.65</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>1487890.7199999997</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="7">
         <v>358599.23999999993</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>368782.32999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="7">
         <v>407029.68</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="7">
         <v>353479.47000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="7">
         <v>1491467.81</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="7">
         <v>368886.83999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="7">
         <v>372044.97000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="7">
         <v>388872.14</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="7">
         <v>361663.86</v>
       </c>
     </row>
@@ -18816,7 +24983,7 @@
       <c r="A17" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="7">
         <v>2421918.17</v>
       </c>
     </row>
@@ -18824,7 +24991,7 @@
       <c r="A18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="7">
         <v>529876.55999999994</v>
       </c>
     </row>
@@ -18832,7 +24999,7 @@
       <c r="A19" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="7">
         <v>522419.16</v>
       </c>
     </row>
@@ -18840,7 +25007,7 @@
       <c r="A20" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="7">
         <v>610347.14999999991</v>
       </c>
     </row>
@@ -18848,7 +25015,7 @@
       <c r="A21" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="7">
         <v>759275.30000000016</v>
       </c>
     </row>
@@ -18856,13 +25023,13 @@
       <c r="A22" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="7">
         <v>6412632.2199999997</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="E5:O5"/>
+    <mergeCell ref="H3:R3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
@@ -18871,79 +25038,213 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB876EF-5F62-42E1-B663-22BF75119CF2}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="7">
         <v>483.40523000000007</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C2" s="7">
+        <v>9776</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="7">
         <v>1368.2435330000003</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C3" s="7">
+        <v>3734</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>1487.9836310000003</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C4" s="7">
+        <v>7551</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>1557.1017999999997</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C5" s="7">
+        <v>9203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="7">
         <v>8336.4585240000015</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C6" s="7">
+        <v>6428</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>22058.841376000004</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C7" s="7">
+        <v>9806</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="7">
         <v>35292.034094000002</v>
+      </c>
+      <c r="C8" s="7">
+        <v>46498</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5207A07B-2A98-42C5-BC0E-8CF2BBE045DB}">
+  <dimension ref="A1:V4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="10"/>
+      <c r="B2" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="10"/>
+      <c r="B3" s="11">
+        <v>6412632.2199999997</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="11">
+        <v>46498</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+    </row>
+    <row r="4" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>